--- a/InputData/elec/RQSD/RPS Qualifying Source Definitions.xlsx
+++ b/InputData/elec/RQSD/RPS Qualifying Source Definitions.xlsx
@@ -1,22 +1,36 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10119"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Meghan\Dropbox (Energy Innovation)\EPS Versions\eps-1.5.0-us-wipI - units progress\InputData\elec\RQSD\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ssy02/Desktop/Postdoc Projects/eps-indonesia-cpl/InputData/elec/RQSD/"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F52575A-BBED-0B48-A9A7-AA32D9789CB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="120" yWindow="135" windowWidth="24915" windowHeight="11565"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="34200" windowHeight="21380" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
     <sheet name="RQSD-BRQSD" sheetId="2" r:id="rId2"/>
     <sheet name="RQSD-RQSD" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -122,7 +136,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -169,14 +183,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -196,9 +209,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -236,9 +249,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -273,7 +286,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -308,7 +321,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -481,80 +494,80 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B18"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="84.59765625" customWidth="1"/>
+    <col min="2" max="2" width="84.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B4" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B5" s="2"/>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>26</v>
       </c>
@@ -566,18 +579,18 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr>
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:B17"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="24.59765625" customWidth="1"/>
-    <col min="2" max="2" width="22.86328125" customWidth="1"/>
+    <col min="1" max="1" width="24.6640625" customWidth="1"/>
+    <col min="2" max="2" width="22.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>2</v>
       </c>
@@ -585,7 +598,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>17</v>
       </c>
@@ -593,7 +606,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>11</v>
       </c>
@@ -601,7 +614,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -609,7 +622,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -617,7 +630,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>18</v>
       </c>
@@ -625,7 +638,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>5</v>
       </c>
@@ -633,7 +646,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>6</v>
       </c>
@@ -641,7 +654,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>7</v>
       </c>
@@ -649,7 +662,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>8</v>
       </c>
@@ -657,7 +670,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>9</v>
       </c>
@@ -665,7 +678,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>10</v>
       </c>
@@ -673,7 +686,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>16</v>
       </c>
@@ -682,7 +695,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>19</v>
       </c>
@@ -690,7 +703,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>28</v>
       </c>
@@ -698,7 +711,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>29</v>
       </c>
@@ -706,7 +719,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>30</v>
       </c>
@@ -720,18 +733,18 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr>
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:B17"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="24.59765625" customWidth="1"/>
-    <col min="2" max="2" width="22.86328125" customWidth="1"/>
+    <col min="1" max="1" width="24.6640625" customWidth="1"/>
+    <col min="2" max="2" width="22.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>2</v>
       </c>
@@ -739,7 +752,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>17</v>
       </c>
@@ -747,7 +760,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>11</v>
       </c>
@@ -755,7 +768,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -763,15 +776,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>4</v>
       </c>
       <c r="B5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.45">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>18</v>
       </c>
@@ -779,7 +792,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>5</v>
       </c>
@@ -787,7 +800,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>6</v>
       </c>
@@ -795,7 +808,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>7</v>
       </c>
@@ -803,7 +816,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>8</v>
       </c>
@@ -811,7 +824,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>9</v>
       </c>
@@ -819,7 +832,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>10</v>
       </c>
@@ -827,7 +840,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>16</v>
       </c>
@@ -836,7 +849,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>19</v>
       </c>
@@ -844,7 +857,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>28</v>
       </c>
@@ -852,7 +865,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>29</v>
       </c>
@@ -860,7 +873,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>30</v>
       </c>
